--- a/Cherrelyn - 100-Day Plan (revised).xlsx
+++ b/Cherrelyn - 100-Day Plan (revised).xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="335">
   <si>
     <t xml:space="preserve">Cherrelyn — Financial Snapshot</t>
   </si>
@@ -151,10 +151,37 @@
     <t xml:space="preserve">   • CHOW / new-system cutover date &amp; owner</t>
   </si>
   <si>
-    <t xml:space="preserve">REVISED FROM THE FULL ACQUISITION P&amp;L  —  8/30/26  (601ch, Mar25–Feb26, accrual)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The snapshot above reconciles exactly to the GL. What the line-level detail changes:</t>
+    <t xml:space="preserve">RESTATED MONTHLY FROM THE FULL ACQUISITION P&amp;L — 8/30/26 (601ch, Mar25–Feb26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The annual figures above reconcile exactly to the GL. Restated per month, with what the line-level detail changes:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit &amp; Loss — per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ / month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual (memo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Total Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Total Operating Expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Adjusted EBITDA (before mgmt fee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Management Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  EBITDAR (rent-coverage pool)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Part B respiratory is ACCELERATING — the TTM basis understates the Day-1 exit</t>
@@ -169,7 +196,7 @@
     <t xml:space="preserve">   Growth over 5 months</t>
   </si>
   <si>
-    <t xml:space="preserve">No corresponding change in census.</t>
+    <t xml:space="preserve">No change in census.</t>
   </si>
   <si>
     <t xml:space="preserve">   TTM monthly average</t>
@@ -178,19 +205,19 @@
     <t xml:space="preserve">A level not seen since December.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Net forgone — TTM basis (what the model carries)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Net forgone — Jan/Feb run-rate basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Understatement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Larger than the entire overtime lever.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Blended Part B realization H1 vs H2</t>
+    <t xml:space="preserve">   Net forgone / month — TTM basis (model as received)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Net forgone / month — Jan/Feb run-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Understatement / month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larger than the monthly overtime lever in every case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Blended Part B realization, H1 / H2</t>
   </si>
   <si>
     <t xml:space="preserve">42.3% / 42.1%</t>
@@ -199,15 +226,27 @@
     <t xml:space="preserve">Rate is stable — the basis is the problem, not the rate.</t>
   </si>
   <si>
+    <t xml:space="preserve">   Respiratory as share of the Part B book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapy Part B is $99,866/mo gross, ~$42,143/mo net. Decide the scope before Day 1.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2. Overtime base is 5.8x the figure this plan named</t>
   </si>
   <si>
     <t xml:space="preserve">   Director OT (5111+5140) — as stated above</t>
   </si>
   <si>
+    <t xml:space="preserve">$234,288/yr</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Building-wide OT, all 24 departments</t>
   </si>
   <si>
+    <t xml:space="preserve">$1,355,761/yr</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Director OT as share of the real base</t>
   </si>
   <si>
@@ -217,13 +256,13 @@
     <t xml:space="preserve">   Building OT % of worked payroll</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirms the 11.3% stated in diligence.</t>
+    <t xml:space="preserve">Confirms the 11.3% in diligence.</t>
   </si>
   <si>
     <t xml:space="preserve">   Nursing OT % of nursing worked payroll</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirms the 15.3% stated in diligence.</t>
+    <t xml:space="preserve">Confirms the 15.3% in diligence.</t>
   </si>
   <si>
     <t xml:space="preserve">   Agency / contract-nursing accounts in the GL</t>
@@ -250,37 +289,19 @@
     <t xml:space="preserve">Model Upside assumed +6. Skilled mix 7.8% (P&amp;L yr) → 12.3% (2026 YTD).</t>
   </si>
   <si>
-    <t xml:space="preserve">   Break-even ADC to offset Part B at run-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAP OF 2.7 ADC (~$256K/yr). Under the old TTM math break-even was 5.1 and this was covered twice over.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. New lever this plan omits — Medicaid case-mix capture (CO135, 10/1/25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Residents on the listing / average CMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162  /  1.7143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Residents below a 1.20 index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Medicaid days per year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   MDS RN labor (5112) against a $20M+ Medicaid book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Illustrative value of +0.05 CMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLACEHOLDER — needs the Colorado nursing-component rate. Do not bank.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Risks now quantified</t>
+    <t xml:space="preserve">   Monthly EBITDAR per added skilled ADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ADC needed to offset Part B at run-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   GAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per month. What overtime reduction has to cover. Under the old TTM math break-even was 5.1 ADC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Risks — per month</t>
   </si>
   <si>
     <t xml:space="preserve">   Private-pay erosion (4,795 days CY23 → 3,529 TTM)</t>
@@ -289,13 +310,22 @@
     <t xml:space="preserve">Masked by Medicaid backfill; occupancy never moved.</t>
   </si>
   <si>
+    <t xml:space="preserve">   Bad debt (5090-4999)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Admin bonus pool (5110-1230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-point at OT and skilled-mix targets.</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Survey: 2567 of 1/30/25 — 5 tags, F880 infection control at E</t>
   </si>
   <si>
     <t xml:space="preserve">OVERDUE</t>
   </si>
   <si>
-    <t xml:space="preserve">Recert 19 months out vs a 9–15 month cycle. An admissions hold hits the skilled census this plan depends on.</t>
+    <t xml:space="preserve">Recert 19 months out vs a 9–15 month cycle.</t>
   </si>
   <si>
     <t xml:space="preserve">   Turnover conflict — profile 37.4% vs prior plan 61%</t>
@@ -304,25 +334,34 @@
     <t xml:space="preserve">RECONCILE</t>
   </si>
   <si>
-    <t xml:space="preserve">The OT case rests on which is true: 37% = scheduling problem, 61% = retention problem.</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Rate assumption: implied Medicare A $383/day vs Medicaid $393/day</t>
   </si>
   <si>
-    <t xml:space="preserve">Model assumes a $400 differential. Confirm real CO rates — the largest single lever depends on it.</t>
+    <t xml:space="preserve">CONFIRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model assumes a $400 differential. Drives the largest lever.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXCLUDED FROM THE MODEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Medicaid case-mix capture — Colorado case-mix will not move the Medicaid rate for roughly two years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Track as an FY28 item. The CO135 listing (162 residents, 1.7143 avg index, 22.2% below 1.20, MDS RN labor $1,033/mo) is worth working on clinical grounds, but it is not a 100-day financial lever.</t>
   </si>
   <si>
     <t xml:space="preserve">STILL CONFIRM DAY ONE (revised)</t>
   </si>
   <si>
-    <t xml:space="preserve">   • Colorado rate sheet: Medicare A / Managed Care / Medicaid per diems + nursing-component rate per CMI point</t>
+    <t xml:space="preserve">   • Colorado rate sheet: Medicare A / Managed Care / Medicaid per diems — validates the largest lever</t>
   </si>
   <si>
     <t xml:space="preserve">   • Actual cash collected on 4543-0040 separated from therapy Part B (42.2% is a blended Part B rate)</t>
   </si>
   <si>
-    <t xml:space="preserve">   • Scope decision in writing: respiratory Part B only, or all Part B (therapy Part B = $1,198,390 gross / ~$505,700 net)</t>
+    <t xml:space="preserve">   • Scope decision in writing: respiratory Part B only, or all Part B (therapy Part B ≈ $42,143/mo net)</t>
   </si>
   <si>
     <t xml:space="preserve">   • Respiratory therapy wind-down cost — severance is excluded from every scenario</t>
@@ -331,13 +370,13 @@
     <t xml:space="preserve">   • Payroll/termination report to settle 37.4% vs 61% turnover</t>
   </si>
   <si>
-    <t xml:space="preserve">   • A/R aging behind the $442,677 bad-debt line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cherrelyn — EBITDAR Bridge (revised)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part B priced off the Jan–Feb 2026 run-rate rather than the TTM average. Skilled-mix lever restated to census already achieved. Case-mix lever added.</t>
+    <t xml:space="preserve">   • A/R aging behind the $36,890/mo bad-debt line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cherrelyn — EBITDAR Bridge (MONTHLY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All figures per month. Part B priced off the Jan–Feb 2026 run-rate rather than the TTM average. Skilled-mix lever restated to census already achieved. Medicaid case-mix EXCLUDED — no rate impact for ~2 years.</t>
   </si>
   <si>
     <t xml:space="preserve">Driver</t>
@@ -355,28 +394,28 @@
     <t xml:space="preserve">Basis</t>
   </si>
   <si>
-    <t xml:space="preserve">Baseline EBITDAR (TTM per P&amp;L)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6100-9999</t>
+    <t xml:space="preserve">Baseline EBITDAR / month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$2,616,869 ÷ 12</t>
   </si>
   <si>
     <t xml:space="preserve">Part B respiratory net forgone</t>
   </si>
   <si>
-    <t xml:space="preserve">3-month / Jan-Feb run-rate gross × 42.2%</t>
+    <t xml:space="preserve">Dec–Feb avg / Jan–Feb run-rate × 42.2%</t>
   </si>
   <si>
     <t xml:space="preserve">Respiratory therapy labor offset</t>
   </si>
   <si>
-    <t xml:space="preserve">60 / 72 / 80% of 5113 labor $347,318</t>
+    <t xml:space="preserve">60 / 72 / 80% of $28,943/mo (GL 5113)</t>
   </si>
   <si>
     <t xml:space="preserve">Overtime reduction</t>
   </si>
   <si>
-    <t xml:space="preserve">11 / 18 / 26% of the $1,355,761 OT base</t>
+    <t xml:space="preserve">11 / 18 / 26% of the $112,980/mo OT base</t>
   </si>
   <si>
     <t xml:space="preserve">Skilled mix — hold the recovery</t>
@@ -385,34 +424,28 @@
     <t xml:space="preserve">50 / 75 / 100% of the +8.6 ADC already won</t>
   </si>
   <si>
-    <t xml:space="preserve">Medicaid case-mix capture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+0.05 CMI illustrative — rate unconfirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total EBITDAR change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRO FORMA EBITDAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original model, same case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From the EBITDAR Impact Model as received.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference (effect of repricing Part B)</t>
+    <t xml:space="preserve">Total monthly EBITDAR change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO FORMA MONTHLY EBITDAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs. baseline month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only the Upside case is accretive to today's monthly run-rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memo — annualized (×12), rent/debt coverage only</t>
   </si>
   <si>
     <t xml:space="preserve">BREAK-EVEN CHECK</t>
   </si>
   <si>
-    <t xml:space="preserve">EBITDAR per added skilled ADC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$400 differential × 365 × 65% margin. RATE UNCONFIRMED.</t>
+    <t xml:space="preserve">Monthly EBITDAR per added skilled ADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$400 differential × 30.4 days × 65% margin. RATE UNCONFIRMED.</t>
   </si>
   <si>
     <t xml:space="preserve">Skilled ADC needed to offset the Part B exit</t>
@@ -430,7 +463,13 @@
     <t xml:space="preserve">GAP</t>
   </si>
   <si>
-    <t xml:space="preserve">What overtime and case-mix capture exist to close.</t>
+    <t xml:space="preserve">Per month. What overtime reduction has to cover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXCLUDED: Medicaid case-mix capture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colorado case-mix will not move the Medicaid rate for roughly two years. Removed from the bridge; track as an FY28 item.</t>
   </si>
   <si>
     <t xml:space="preserve">Cherrelyn — Executive Director 100-Day Plan</t>
@@ -460,7 +499,7 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">EBITDAR Impact ($/yr)</t>
+    <t xml:space="preserve">EBITDAR Impact ($/month)</t>
   </si>
   <si>
     <t xml:space="preserve">Days 1–30
@@ -485,7 +524,7 @@
     <t xml:space="preserve">Not started</t>
   </si>
   <si>
-    <t xml:space="preserve">CHOW — protects all of it</t>
+    <t xml:space="preserve">Protects all of it</t>
   </si>
   <si>
     <t xml:space="preserve">People &amp; Team</t>
@@ -527,7 +566,7 @@
     <t xml:space="preserve">Medicaid-pending and &gt;90-day AR quantified</t>
   </si>
   <si>
-    <t xml:space="preserve">Bad debt $442,677</t>
+    <t xml:space="preserve">Bad debt $36,890/mo</t>
   </si>
   <si>
     <t xml:space="preserve">Census &amp; Payer Mix</t>
@@ -542,7 +581,7 @@
     <t xml:space="preserve">Referral-source list + barriers documented</t>
   </si>
   <si>
-    <t xml:space="preserve">Skilled ADC worth $94,900 each</t>
+    <t xml:space="preserve">$7,908 per skilled ADC</t>
   </si>
   <si>
     <t xml:space="preserve">Days 31–60
@@ -558,10 +597,13 @@
     <t xml:space="preserve">≥2 new/renewed referral relationships; skilled admits trending up</t>
   </si>
   <si>
-    <t xml:space="preserve">$408K – $816K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stand up MDS/case-mix accuracy audit; tighten triple-check and ADL capture.</t>
+    <t xml:space="preserve">$34,006 – $68,012/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REMOVED] MDS/case-mix accuracy audit. Colorado case-mix will not move the Medicaid rate for ~2 years — not a 100-day financial lever. Track as FY28.</t>
   </si>
   <si>
     <t xml:space="preserve">MDS RN labor only $12K vs $20M+ Medicaid; case-mix = rate</t>
@@ -570,7 +612,10 @@
     <t xml:space="preserve">Case-mix index baseline + audit cadence; rate uplift identified</t>
   </si>
   <si>
-    <t xml:space="preserve">$0 – $314K illustrative</t>
+    <t xml:space="preserve">Removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case mix REMOVED — FY28 item</t>
   </si>
   <si>
     <t xml:space="preserve">Attack overtime: schedule rebuild, fill key vacancies, reduce agency reliance.</t>
@@ -582,7 +627,7 @@
     <t xml:space="preserve">OT $ down vs baseline; vacancy rate down</t>
   </si>
   <si>
-    <t xml:space="preserve">$150K – $350K</t>
+    <t xml:space="preserve">$12,500 – $29,167/mo</t>
   </si>
   <si>
     <t xml:space="preserve">Drive Medicaid-pending conversions and private-pay collection workflow.</t>
@@ -628,7 +673,7 @@
     <t xml:space="preserve">Approved budget; rent/debt coverage modeled</t>
   </si>
   <si>
-    <t xml:space="preserve">Rent coverage on $2.24M – $3.05M</t>
+    <t xml:space="preserve">Coverage on $187K – $228K/mo</t>
   </si>
   <si>
     <t xml:space="preserve">Lock leadership: succession/development for DON, MDS, Therapy, Business Office. Confirm incentive plans.</t>
@@ -640,7 +685,7 @@
     <t xml:space="preserve">Development plans + aligned incentive structure</t>
   </si>
   <si>
-    <t xml:space="preserve">$225K bonus pool re-pointed</t>
+    <t xml:space="preserve">$18,787/mo bonus pool</t>
   </si>
   <si>
     <t xml:space="preserve">Set quality roadmap to protect/raise star rating (key to MA &amp; referrals).</t>
@@ -664,7 +709,7 @@
     <t xml:space="preserve">Live monthly KPI dashboard</t>
   </si>
   <si>
-    <t xml:space="preserve">ADDED FROM FULL P&amp;L DILIGENCE — 8/30/26</t>
+    <t xml:space="preserve">ADDED FROM FULL P&amp;L DILIGENCE — 8/30/26 (all impacts monthly)</t>
   </si>
   <si>
     <t xml:space="preserve">Financial / Part B</t>
@@ -673,70 +718,58 @@
     <t xml:space="preserve">CRITICAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Stop billing Medicare Part B respiratory (4543-0040) at close. Decide IN WRITING whether the exit covers therapy Part B (4544/4545/4546-0040) as well. Wind down RT labor against the 72% of respiratory revenue Part B represented; cost the severance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross billing tripled Sep 25 → Feb 26 ($93,700 → $284,775). TTM basis understates the exit by up to $589,176.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billing stopped Day 1; scope decision documented; wind-down plan costed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">($1.07M) net of RT offset</t>
+    <t xml:space="preserve">Stop billing Medicare Part B respiratory (4543-0040) at close. Decide IN WRITING whether the exit covers therapy Part B (4544/4545/4546-0040). Wind down RT labor against the 72% of respiratory revenue Part B represented; cost the severance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross billing tripled Sep 25 → Feb 26 ($93,700 → $284,775/mo). TTM basis understates the exit by $49,098/mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billing stopped Day 1; scope decision documented; wind-down costed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">($89,540)/mo net of RT offset</t>
   </si>
   <si>
     <t xml:space="preserve">Financial / Rate Confirmation</t>
   </si>
   <si>
-    <t xml:space="preserve">Obtain the Colorado rate sheet: Medicare A, Managed Care and Medicaid per diems, plus nursing-component rate per case-mix point.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model assumes a $400/day differential; P&amp;L ÷ census days implies $383 Medicare A vs $393 Medicaid. The largest lever is unverified.</t>
+    <t xml:space="preserve">Obtain the Colorado rate sheet: Medicare A, Managed Care and Medicaid per diems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model assumes $400/day differential; P&amp;L ÷ census days implies $383 Medicare A vs $393 Medicaid. The largest lever is unverified.</t>
   </si>
   <si>
     <t xml:space="preserve">Real per diems confirmed; bridge restated</t>
   </si>
   <si>
-    <t xml:space="preserve">Validates $408K – $816K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule rebuild reaching the CNA line — $452,339 of OT sits there, a third of the building total. Fill the vacancies driving OT BEFORE cutting OT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building OT is $1,355,761 across 24 departments — 5.8x the $234K director figure. No agency account exists in the GL.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT tracked weekly by department vs the $1.36M base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial / Case Mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart-audit the 36 residents below a 1.20 case-mix index against ADL/Section GG, restorative and behavior coding. Resource the MDS function.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO135: 162 residents at 1.7143 avg; 22.2% below 1.20. MDS RN labor only $12,399/yr against 54,326 Medicaid days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low-index cohort audited; CMI baseline + audit cadence set</t>
+    <t xml:space="preserve">Validates $34K – $68K/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule rebuild reaching the CNA line — $37,695/mo of OT sits there, a third of the building total. Fill the vacancies driving OT BEFORE cutting OT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building OT is $112,980/mo across 24 departments — 5.8x the $19,524/mo director figure. No agency account exists in the GL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT tracked weekly by department vs the $112,980/mo base</t>
   </si>
   <si>
     <t xml:space="preserve">Diagnose private-pay erosion before setting a target: referral drift, rate position, or faster Medicaid conversion.</t>
   </si>
   <si>
-    <t xml:space="preserve">Private days fell 4,795 (CY23) → 3,529 (TTM) = −1,266 days ≈ $514K at the $406 implied rate. Hidden by Medicaid backfill.</t>
+    <t xml:space="preserve">Private days fell 4,795 (CY23) → 3,529 (TTM) ≈ $42,856/mo at the $406 implied rate. Hidden by Medicaid backfill.</t>
   </si>
   <si>
     <t xml:space="preserve">Cause named; stabilization target set</t>
   </si>
   <si>
-    <t xml:space="preserve">($514K) exposure</t>
+    <t xml:space="preserve">($42,856)/mo exposure</t>
   </si>
   <si>
     <t xml:space="preserve">Reinstate the F880 infection-control audit cadence (EBP gown/glove, pre-meal hand hygiene). Mock survey against all five 2567 tags by day 21.</t>
   </si>
   <si>
-    <t xml:space="preserve">2567 of 1/30/25: 5 tags, F880 at scope E. Recert is 19 months out against a 9–15 month cycle — overdue.</t>
+    <t xml:space="preserve">2567 of 1/30/25: 5 tags, F880 at scope E. Recert 19 months out against a 9–15 month cycle — overdue.</t>
   </si>
   <si>
     <t xml:space="preserve">Mock survey complete; audit cadence live</t>
@@ -745,16 +778,13 @@
     <t xml:space="preserve">Protects the skilled census</t>
   </si>
   <si>
-    <t xml:space="preserve">Rebuild the FY budget on the ACTUAL post-exit run-rate, not the TTM P&amp;L. Model rent and debt service against pro-forma EBITDAR of $2.24M–$3.05M, not the $2.62M baseline.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro forma is $2,241,651 / $2,561,467 / $3,050,265 — the Base case is essentially flat to today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approved budget; rent/debt coverage modeled on post-exit reality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coverage on $2.24M – $3.05M</t>
+    <t xml:space="preserve">Rebuild the FY budget on the ACTUAL post-exit MONTHLY run-rate, not the TTM P&amp;L. Model rent and debt service against $186,804 – $228,026/mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base case is $200,374/mo against a $218,072/mo baseline — a $17,698/mo decline. Only Upside is accretive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved budget on post-exit monthly reality</t>
   </si>
   <si>
     <t xml:space="preserve">Cherrelyn — Week-by-Week 100-Day Calendar</t>
@@ -1142,15 +1172,15 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="16"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1257,7 +1287,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1310,7 +1340,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1322,35 +1368,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1366,15 +1396,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1382,7 +1408,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1411,6 +1437,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1686,7 +1720,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1992,7 +2026,7 @@
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
         <v>43</v>
       </c>
@@ -2001,360 +2035,481 @@
       <c r="A45" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
+      <c r="B45" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="17" t="n">
+      <c r="A46" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="16" t="n">
+        <f aca="false">24211360/12</f>
+        <v>2017613.33333333</v>
+      </c>
+      <c r="C46" s="17" t="n">
+        <f aca="false">B46/$B$46</f>
+        <v>1</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>24211360</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="16" t="n">
+        <f aca="false">20302792/12</f>
+        <v>1691899.33333333</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <f aca="false">B47/$B$46</f>
+        <v>0.838564706815313</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>20302792</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="16" t="n">
+        <f aca="false">3908569/12</f>
+        <v>325714.083333333</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <f aca="false">B48/$B$46</f>
+        <v>0.161435334487612</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>3908569</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="16" t="n">
+        <f aca="false">1291699/12</f>
+        <v>107641.583333333</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <f aca="false">B49/$B$46</f>
+        <v>0.0533509476543243</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>1291699</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="16" t="n">
+        <f aca="false">2616869/12</f>
+        <v>218072.416666667</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <f aca="false">B50/$B$46</f>
+        <v>0.108084345530363</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>2616869</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="20" t="n">
         <v>93700</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="17" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="20" t="n">
         <v>284775</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="18" t="n">
-        <f aca="false">B47/B46-1</f>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="17" t="n">
+        <f aca="false">B54/B53-1</f>
         <v>2.03922091782284</v>
       </c>
-      <c r="D48" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="20" t="n">
+      <c r="D55" s="21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="16" t="n">
         <f aca="false">1742597/12</f>
         <v>145216.416666667</v>
       </c>
-      <c r="D49" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="20" t="n">
-        <f aca="false">1742597*0.422</f>
-        <v>735375.934</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="22" t="n">
-        <f aca="false">3138750*0.422</f>
-        <v>1324552.5</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" s="22" t="n">
-        <f aca="false">B51-B50</f>
-        <v>589176.566</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="16" t="s">
+      <c r="D56" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="17" t="n">
-        <v>234288</v>
-      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="23" t="n">
-        <v>1355761</v>
+      <c r="B57" s="16" t="n">
+        <f aca="false">B56*0.422</f>
+        <v>61281.3278333333</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="18" t="n">
-        <f aca="false">B56/B57</f>
+      <c r="B58" s="22" t="n">
+        <f aca="false">261562*0.422</f>
+        <v>110379.164</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="22" t="n">
+        <f aca="false">B58-B57</f>
+        <v>49097.8361666667</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="17" t="n">
+        <f aca="false">1742597/(1742597+1198390)</f>
+        <v>0.592521150212497</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="16" t="n">
+        <f aca="false">234288/12</f>
+        <v>19524</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="23" t="n">
+        <f aca="false">1355761/12</f>
+        <v>112980.083333333</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="17" t="n">
+        <f aca="false">B64/B65</f>
         <v>0.172809219324055</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59" s="17" t="n">
-        <v>452339</v>
-      </c>
-      <c r="C59" s="18" t="n">
-        <f aca="false">B59/B57</f>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="16" t="n">
+        <f aca="false">452339/12</f>
+        <v>37694.9166666667</v>
+      </c>
+      <c r="C67" s="17" t="n">
+        <f aca="false">B67/B65</f>
         <v>0.333642138990574</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" s="18" t="n">
-        <f aca="false">B57/(B57+10454987)</f>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="17" t="n">
+        <f aca="false">1355761/(1355761+10454987)</f>
         <v>0.114790443416454</v>
       </c>
-      <c r="D60" s="19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B61" s="18" t="n">
+      <c r="D68" s="21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69" s="17" t="n">
         <f aca="false">1117862/(1117862+6035723)</f>
         <v>0.156265984118453</v>
       </c>
-      <c r="D61" s="19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="24" t="n">
+      <c r="D69" s="21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="19"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" s="24" t="n">
         <v>13.4</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="24" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B74" s="24" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="25" t="n">
-        <f aca="false">B66-B65</f>
+    <row r="75" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75" s="25" t="n">
+        <f aca="false">B74-B73</f>
         <v>8.6</v>
       </c>
-      <c r="D67" s="19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="26" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" s="27" t="n">
-        <v>36</v>
-      </c>
-      <c r="C72" s="18" t="n">
-        <f aca="false">B72/162</f>
-        <v>0.222222222222222</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B73" s="27" t="n">
-        <v>54326</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" s="17" t="n">
-        <v>12399</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B75" s="20" t="n">
-        <f aca="false">0.05/1.7001*0.5*393*B73</f>
-        <v>313953.85565555</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>84</v>
+      <c r="D75" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B76" s="16" t="n">
+        <f aca="false">400*(365/12)*0.65</f>
+        <v>7908.33333333333</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78" s="20" t="n">
-        <f aca="false">-1266*406</f>
-        <v>-513996</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B79" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D79" s="19" t="s">
+      <c r="B77" s="26" t="n">
+        <f aca="false">(B58-347318/12*0.72)/B76</f>
+        <v>11.3222445521602</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="14" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="16" t="s">
+      <c r="B78" s="26" t="n">
+        <f aca="false">B75-B77</f>
+        <v>-2.72224455216017</v>
+      </c>
+      <c r="C78" s="22" t="n">
+        <f aca="false">B78*B76</f>
+        <v>-21528.4173333333</v>
+      </c>
+      <c r="D78" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="16" t="s">
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D80" s="19" t="s">
+      <c r="B80" s="19"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="15" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="16" t="s">
+      <c r="B81" s="16" t="n">
+        <f aca="false">-514274/12</f>
+        <v>-42856.1666666667</v>
+      </c>
+      <c r="D81" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D81" s="19" t="s">
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="15" t="s">
         <v>95</v>
       </c>
+      <c r="B82" s="16" t="n">
+        <f aca="false">-442677/12</f>
+        <v>-36889.75</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
+      <c r="B83" s="16" t="n">
+        <f aca="false">225442/12</f>
+        <v>18786.8333333333</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="16" t="s">
-        <v>97</v>
+      <c r="A84" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B84" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="16" t="s">
-        <v>98</v>
+      <c r="A85" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="16" t="s">
-        <v>100</v>
+      <c r="A86" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="16" t="s">
-        <v>102</v>
+      <c r="A88" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+    </row>
+    <row r="89" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="15" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2373,269 +2528,280 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>2616869</v>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>2616869</v>
-      </c>
-      <c r="D5" s="20" t="n">
-        <v>2616869</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>111</v>
+      <c r="A5" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="16" t="n">
+        <f aca="false">2616869/12</f>
+        <v>218072.416666667</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <f aca="false">2616869/12</f>
+        <v>218072.416666667</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <f aca="false">2616869/12</f>
+        <v>218072.416666667</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="20" t="n">
-        <v>-1141679</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>-1324552</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>-1324552</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>113</v>
+      <c r="A6" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <f aca="false">-225450*0.422</f>
+        <v>-95139.9</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <f aca="false">-261562*0.422</f>
+        <v>-110379.164</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <f aca="false">-261562*0.422</f>
+        <v>-110379.164</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="20" t="n">
-        <v>208391</v>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>250069</v>
-      </c>
-      <c r="D7" s="20" t="n">
-        <v>277854</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>115</v>
+      <c r="A7" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="16" t="n">
+        <f aca="false">347318/12*0.6</f>
+        <v>17365.9</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <f aca="false">347318/12*0.72</f>
+        <v>20839.08</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <f aca="false">347318/12*0.8</f>
+        <v>23154.5333333333</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="20" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>350000</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>117</v>
+      <c r="A8" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <f aca="false">150000/12</f>
+        <v>12500</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <f aca="false">250000/12</f>
+        <v>20833.3333333333</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <f aca="false">350000/12</f>
+        <v>29166.6666666667</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="20" t="n">
-        <v>408070</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <v>612105</v>
-      </c>
-      <c r="D9" s="20" t="n">
-        <v>816140</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>119</v>
+      <c r="A9" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <f aca="false">8.6*0.5*400*(365/12)*0.65</f>
+        <v>34005.8333333333</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <f aca="false">8.6*0.75*400*(365/12)*0.65</f>
+        <v>51008.75</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">8.6*1*400*(365/12)*0.65</f>
+        <v>68011.6666666667</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>156977</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>313954</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>121</v>
+      <c r="A10" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="23" t="n">
+        <f aca="false">SUM(B6:B9)</f>
+        <v>-31268.1666666667</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <f aca="false">SUM(C6:C9)</f>
+        <v>-17698.0006666667</v>
+      </c>
+      <c r="D10" s="23" t="n">
+        <f aca="false">SUM(D6:D9)</f>
+        <v>9953.70266666669</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>122</v>
+      <c r="A11" s="14" t="s">
+        <v>134</v>
       </c>
       <c r="B11" s="29" t="n">
-        <f aca="false">SUM(B6:B10)</f>
-        <v>-375218</v>
+        <f aca="false">B5+B10</f>
+        <v>186804.25</v>
       </c>
       <c r="C11" s="29" t="n">
-        <f aca="false">SUM(C6:C10)</f>
-        <v>-55401</v>
+        <f aca="false">C5+C10</f>
+        <v>200374.416</v>
       </c>
       <c r="D11" s="29" t="n">
-        <f aca="false">SUM(D6:D10)</f>
-        <v>433396</v>
+        <f aca="false">D5+D10</f>
+        <v>228026.119333333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="30" t="n">
-        <f aca="false">B5+B11</f>
+      <c r="A12" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" s="23" t="n">
+        <f aca="false">B11-B5</f>
+        <v>-31268.1666666667</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <f aca="false">C11-C5</f>
+        <v>-17698.0006666667</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <f aca="false">D11-D5</f>
+        <v>9953.70266666668</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <f aca="false">B11*12</f>
         <v>2241651</v>
       </c>
-      <c r="C12" s="30" t="n">
-        <f aca="false">C5+C11</f>
-        <v>2561468</v>
-      </c>
-      <c r="D12" s="30" t="n">
-        <f aca="false">D5+D11</f>
-        <v>3050265</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="20" t="n">
-        <v>2429684</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <v>2761162</v>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>3078747</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="22" t="n">
-        <f aca="false">B12-B13</f>
-        <v>-188033</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <f aca="false">C12-C13</f>
-        <v>-199694</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <f aca="false">D12-D13</f>
-        <v>-28482</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
+      <c r="C13" s="16" t="n">
+        <f aca="false">C11*12</f>
+        <v>2404492.992</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">D11*12</f>
+        <v>2736313.432</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="16" t="n">
+        <f aca="false">400*(365/12)*0.65</f>
+        <v>7908.33333333333</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="B17" s="20" t="n">
-        <f aca="false">400*365*0.65</f>
-        <v>94900</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>129</v>
+      <c r="A17" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <f aca="false">-(C6+C7)/$B$16</f>
+        <v>11.3222445521602</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="26" t="n">
-        <f aca="false">-(C6+C7)/$B$17</f>
-        <v>11.3222655426765</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>131</v>
+      <c r="A18" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="26" t="n">
-        <f aca="false">B19-B18</f>
-        <v>-2.7222655426765</v>
-      </c>
-      <c r="C20" s="22" t="n">
-        <f aca="false">B20*$B$17</f>
-        <v>-258343</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>135</v>
+      <c r="A19" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="26" t="n">
+        <f aca="false">B18-B17</f>
+        <v>-2.72224455216017</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <f aca="false">B19*$B$16</f>
+        <v>-21528.4173333333</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2654,7 +2820,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="18"/>
@@ -2662,429 +2828,429 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>144</v>
+      <c r="A4" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>157</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>153</v>
+      <c r="A5" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>152</v>
+      <c r="A6" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" s="34" t="s">
+      <c r="A7" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="F7" s="34" t="s">
+      <c r="B7" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="G7" s="36" t="s">
-        <v>152</v>
+      <c r="D7" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="E8" s="34" t="s">
+      <c r="A8" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="F8" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="B12" s="33" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="F9" s="34" t="s">
+      <c r="C12" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="G9" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="E10" s="34" t="s">
+      <c r="C14" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="C16" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="G10" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>201</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>203</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>204</v>
+      <c r="D17" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="F18" s="34" t="s">
+      <c r="A18" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H18" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="G18" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>192</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="B19" s="34" t="s">
+      <c r="A19" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="C19" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>211</v>
-      </c>
-      <c r="G19" s="36" t="s">
-        <v>152</v>
+      <c r="B19" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -3095,185 +3261,159 @@
       <c r="H20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D21" s="19" t="s">
+      <c r="A21" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H26" s="21" t="s">
         <v>215</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="C22" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3305,332 +3445,332 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>249</v>
+      <c r="A4" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>254</v>
+      <c r="A5" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="41" t="s">
-        <v>255</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>256</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>257</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>259</v>
+      <c r="A6" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>263</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>264</v>
+      <c r="A7" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>269</v>
+      <c r="A8" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>273</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>274</v>
+      <c r="A9" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>277</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>278</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>279</v>
+      <c r="A10" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
-        <v>280</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>284</v>
+      <c r="A11" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="s">
-        <v>285</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>286</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>287</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>288</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>289</v>
+      <c r="A12" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>292</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>293</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>294</v>
+      <c r="A13" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="43" t="s">
-        <v>295</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>296</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>297</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>298</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>299</v>
+      <c r="A14" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="s">
-        <v>300</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>304</v>
+      <c r="A15" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="s">
-        <v>305</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>306</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>307</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>308</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>309</v>
+      <c r="A16" s="44" t="s">
+        <v>315</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>311</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>313</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>314</v>
+      <c r="A17" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="43" t="s">
-        <v>315</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>316</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>317</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>318</v>
-      </c>
-      <c r="F18" s="34" t="s">
-        <v>319</v>
+      <c r="A18" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="43" t="s">
-        <v>320</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>321</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>322</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>323</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>324</v>
+      <c r="A19" s="44" t="s">
+        <v>330</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>333</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
